--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,15 +19,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchState</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -798,154 +915,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:H35"/>
+  <x:dimension ref="A1:I35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.4296875" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="19.54296875" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="41.5703125" style="1" customWidth="1"/>
-    <x:col min="4" max="6" width="20.26953125" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="30.54296875" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <x:col min="10" max="12" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="15.71484375" style="1" customWidth="1"/>
-    <x:col min="14" max="14" width="17.4296875" style="1" customWidth="1"/>
-    <x:col min="15" max="16384" width="12.54296875" style="1"/>
+    <x:col min="1" max="2" width="25.4296875" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="25.71484375" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="41.5703125" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="26.85546875" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="23.4296875" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="20.26953125" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="26.54296875" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <x:col min="11" max="13" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="14" width="15.71484375" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="17.4296875" style="1" customWidth="1"/>
+    <x:col min="16" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A5" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A6" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A10" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A11" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A12" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:1" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2" s="7" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="C12" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A13" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A14" s="6" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A15" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A16" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A17" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B3" s="2"/>
-    </x:row>
-    <x:row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="H4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="3"/>
-    </x:row>
-    <x:row r="6" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5"/>
-      <x:c r="B8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5"/>
-    </x:row>
-    <x:row r="10" ht="15.75" customHeight="1"/>
-    <x:row r="11" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-    </x:row>
-    <x:row r="13" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3"/>
-    </x:row>
-    <x:row r="14" ht="15.75" customHeight="1"/>
-    <x:row r="15" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A16" s="5"/>
-      <x:c r="B16" s="5"/>
-    </x:row>
-    <x:row r="17" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A17" s="5"/>
-      <x:c r="B17" s="5"/>
-    </x:row>
-    <x:row r="18" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="B17" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A18" s="5"/>
       <x:c r="B18" s="5"/>
-    </x:row>
-    <x:row r="19" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C18" s="5"/>
+    </x:row>
+    <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A19" s="5"/>
       <x:c r="B19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C19" s="5"/>
+    </x:row>
+    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A20" s="5"/>
       <x:c r="B20" s="5"/>
-    </x:row>
-    <x:row r="21" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C20" s="5"/>
+    </x:row>
+    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A21" s="5"/>
       <x:c r="B21" s="5"/>
-    </x:row>
-    <x:row r="22" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C21" s="5"/>
+    </x:row>
+    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A22" s="5"/>
       <x:c r="B22" s="5"/>
-    </x:row>
-    <x:row r="23" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C22" s="5"/>
+    </x:row>
+    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A23" s="5"/>
       <x:c r="B23" s="5"/>
-    </x:row>
-    <x:row r="24" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C23" s="5"/>
+    </x:row>
+    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A24" s="5"/>
       <x:c r="B24" s="5"/>
-    </x:row>
-    <x:row r="25" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C24" s="5"/>
+    </x:row>
+    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A25" s="5"/>
       <x:c r="B25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A26" s="6"/>
       <x:c r="B26" s="6"/>
-    </x:row>
-    <x:row r="27" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C26" s="6"/>
+    </x:row>
+    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A27" s="6"/>
       <x:c r="B27" s="6"/>
-    </x:row>
-    <x:row r="28" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C27" s="6"/>
+    </x:row>
+    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A28" s="6"/>
       <x:c r="B28" s="6"/>
-    </x:row>
-    <x:row r="29" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C28" s="6"/>
+    </x:row>
+    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A29" s="6"/>
       <x:c r="B29" s="6"/>
-    </x:row>
-    <x:row r="30" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C29" s="6"/>
+    </x:row>
+    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A30" s="6"/>
       <x:c r="B30" s="6"/>
-    </x:row>
-    <x:row r="31" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C30" s="6"/>
+    </x:row>
+    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A31" s="6"/>
       <x:c r="B31" s="6"/>
-    </x:row>
-    <x:row r="32" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C31" s="6"/>
+    </x:row>
+    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A32" s="3"/>
       <x:c r="B32" s="3"/>
-    </x:row>
-    <x:row r="33" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C32" s="3"/>
+    </x:row>
+    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A33" s="3"/>
       <x:c r="B33" s="3"/>
-    </x:row>
-    <x:row r="34" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C33" s="3"/>
+    </x:row>
+    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A34" s="3"/>
       <x:c r="B34" s="3"/>
-    </x:row>
-    <x:row r="35" spans="1:2" ht="15.75" customHeight="1">
+      <x:c r="C34" s="3"/>
+    </x:row>
+    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A35" s="3"/>
       <x:c r="B35" s="3"/>
+      <x:c r="C35" s="3"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -21,130 +21,130 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
   <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>use_uppercut_03</x:t>
   </x:si>
   <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
     <x:t>use_elbow_03</x:t>
   </x:si>
   <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchState</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
     <x:t>TakedownAttempt</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_02</x:t>
-  </x:si>
-  <x:si>
     <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -935,219 +935,219 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>16</x:v>
@@ -1156,58 +1156,58 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>16</x:v>
@@ -1216,47 +1216,47 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,66 +19,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="42">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
+  <x:si>
+    <x:t>use_jab_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
   <x:si>
     <x:t>Wrestling</x:t>
   </x:si>
   <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
     <x:t>HalfGuard</x:t>
   </x:si>
   <x:si>
-    <x:t>Attacker</x:t>
+    <x:t>Standing</x:t>
   </x:si>
   <x:si>
     <x:t>skill_elbow</x:t>
   </x:si>
   <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
   </x:si>
   <x:si>
     <x:t>use_guillotine_01</x:t>
@@ -87,64 +108,49 @@
     <x:t>WrestlingSituation</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_takedown_judo</x:t>
   </x:si>
   <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
   </x:si>
   <x:si>
     <x:t>use_takedown_judo_02</x:t>
   </x:si>
   <x:si>
     <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -935,67 +941,67 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
@@ -1004,219 +1010,219 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
@@ -1224,19 +1230,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
@@ -1244,25 +1250,40 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A18" s="5" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
+      <x:c r="B18" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="5"/>
-      <x:c r="B18" s="5"/>
-      <x:c r="C18" s="5"/>
     </x:row>
     <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A19" s="5"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13035"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,138 +19,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+  <x:si>
+    <x:t>use_takedown_basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
   <x:si>
     <x:t>use_jab_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_jab</x:t>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
   </x:si>
   <x:si>
     <x:t>use_ground_pounding_03</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_02</x:t>
   </x:si>
   <x:si>
     <x:t>use_ground_pounding_02</x:t>
   </x:si>
   <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
+    <x:t>skill_takedown_basic</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -921,7 +927,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I35"/>
+  <x:dimension ref="A1:I36"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="2" width="25.4296875" style="1" customWidth="1"/>
@@ -941,188 +947,188 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A10" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
@@ -1130,165 +1136,180 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
+      <x:c r="A12" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>37</x:v>
+      <x:c r="A15" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C17" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C17" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A19" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B19" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A18" s="5" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A19" s="5"/>
-      <x:c r="B19" s="5"/>
-      <x:c r="C19" s="5"/>
+      <x:c r="C19" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A20" s="5"/>
@@ -1321,9 +1342,9 @@
       <x:c r="C25" s="5"/>
     </x:row>
     <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="6"/>
-      <x:c r="B26" s="6"/>
-      <x:c r="C26" s="6"/>
+      <x:c r="A26" s="5"/>
+      <x:c r="B26" s="5"/>
+      <x:c r="C26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A27" s="6"/>
@@ -1351,9 +1372,9 @@
       <x:c r="C31" s="6"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="3"/>
-      <x:c r="B32" s="3"/>
-      <x:c r="C32" s="3"/>
+      <x:c r="A32" s="6"/>
+      <x:c r="B32" s="6"/>
+      <x:c r="C32" s="6"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A33" s="3"/>
@@ -1370,7 +1391,11 @@
       <x:c r="B35" s="3"/>
       <x:c r="C35" s="3"/>
     </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A36" s="3"/>
+      <x:c r="B36" s="3"/>
+      <x:c r="C36" s="3"/>
+    </x:row>
     <x:row r="37" ht="15.75" customHeight="1"/>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>
@@ -2335,6 +2360,7 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
+    <x:row r="1001" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,144 +19,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="48">
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_jab_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_entry_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
   <x:si>
     <x:t>use_takedown_basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_jab_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -947,374 +953,389 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B19" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B19" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C19" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="5"/>
-      <x:c r="B20" s="5"/>
-      <x:c r="C20" s="5"/>
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A20" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A21" s="5"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,7 +19,118 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="48">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="50">
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_jab_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_entry_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
   <x:si>
     <x:t>use_elbow_03</x:t>
   </x:si>
@@ -27,142 +138,37 @@
     <x:t>TakedownAttempt</x:t>
   </x:si>
   <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
     <x:t>MatchSituation</x:t>
   </x:si>
   <x:si>
     <x:t>use_uppercut_03</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_jab_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_entry_01</x:t>
+    <x:t>use_takedown_basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_escape_01</x:t>
   </x:si>
   <x:si>
     <x:t>use_takedown_judo_02</x:t>
   </x:si>
   <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>use_ground_pounding_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_basic_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -953,179 +959,179 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
         <x:v>24</x:v>
@@ -1134,58 +1140,58 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
         <x:v>24</x:v>
@@ -1194,58 +1200,58 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>24</x:v>
@@ -1254,58 +1260,58 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>24</x:v>
@@ -1314,18 +1320,18 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="C20" s="5" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>24</x:v>
@@ -1334,13 +1340,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="5"/>
-      <x:c r="B21" s="5"/>
-      <x:c r="C21" s="5"/>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A21" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A22" s="5"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,156 +19,189 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="50">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="61">
+  <x:si>
+    <x:t>use_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
     <x:t>Any</x:t>
   </x:si>
   <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_entry_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guard_pass_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_back_control_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_jab_01</x:t>
   </x:si>
   <x:si>
     <x:t>Wrestling</x:t>
   </x:si>
   <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_jab_01</x:t>
+    <x:t>Standing</x:t>
   </x:si>
   <x:si>
     <x:t>skill_jab</x:t>
   </x:si>
   <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_entry_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_escape_01</x:t>
   </x:si>
   <x:si>
     <x:t>use_takedown_basic_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_escape_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_04</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -939,7 +972,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I36"/>
+  <x:dimension ref="A1:I37"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="2" width="25.4296875" style="1" customWidth="1"/>
@@ -959,439 +992,529 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A11" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A11" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="s">
-        <x:v>10</x:v>
+      <x:c r="A13" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C14" s="3" t="s">
-        <x:v>6</x:v>
+      <x:c r="C14" s="6" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>23</x:v>
+      <x:c r="C15" s="3" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A16" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A16" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C17" s="5" t="s">
-        <x:v>6</x:v>
+      <x:c r="C17" s="1" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A19" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="s">
-        <x:v>9</x:v>
+      <x:c r="A19" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A21" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C21" s="5" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A22" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B21" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C21" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
+    </x:row>
+    <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A23" s="5" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="5"/>
-      <x:c r="B22" s="5"/>
-      <x:c r="C22" s="5"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="5"/>
-      <x:c r="B23" s="5"/>
-      <x:c r="C23" s="5"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="5"/>
-      <x:c r="B24" s="5"/>
-      <x:c r="C24" s="5"/>
-    </x:row>
-    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="5"/>
-      <x:c r="B25" s="5"/>
-      <x:c r="C25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="5"/>
-      <x:c r="B26" s="5"/>
-      <x:c r="C26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="6"/>
-      <x:c r="B27" s="6"/>
-      <x:c r="C27" s="6"/>
+      <x:c r="F23" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A24" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B24" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C24" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A25" s="5" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A26" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B26" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C26" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A27" s="5" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B27" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C27" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A28" s="6"/>
@@ -1419,9 +1542,9 @@
       <x:c r="C32" s="6"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="3"/>
-      <x:c r="B33" s="3"/>
-      <x:c r="C33" s="3"/>
+      <x:c r="A33" s="6"/>
+      <x:c r="B33" s="6"/>
+      <x:c r="C33" s="6"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A34" s="3"/>
@@ -1438,7 +1561,11 @@
       <x:c r="B36" s="3"/>
       <x:c r="C36" s="3"/>
     </x:row>
-    <x:row r="37" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A37" s="3"/>
+      <x:c r="B37" s="3"/>
+      <x:c r="C37" s="3"/>
+    </x:row>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>
     <x:row r="40" ht="15.75" customHeight="1"/>
@@ -2403,6 +2530,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
     <x:row r="1001" ht="15.75" customHeight="1"/>
+    <x:row r="1002" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,12 +19,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="61">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="66">
+  <x:si>
+    <x:t>use_ground_escape_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_entry_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_back_control_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guard_pass_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_01</x:t>
+  </x:si>
   <x:si>
     <x:t>use_halfguard_pass</x:t>
   </x:si>
   <x:si>
-    <x:t>use_ground_sweep_01</x:t>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_03</x:t>
   </x:si>
   <x:si>
     <x:t>UserRole</x:t>
@@ -36,172 +102,121 @@
     <x:t>Attacker</x:t>
   </x:si>
   <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_jab_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_escape_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_halfguard_pass</x:t>
   </x:si>
   <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_entry_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guard_pass_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_back_control_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_jab_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_ground_pounding</x:t>
   </x:si>
   <x:si>
     <x:t>use_ground_pounding_03</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
+    <x:t>use_takedown_basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_04</x:t>
   </x:si>
   <x:si>
     <x:t>use_takedown_judo_02</x:t>
   </x:si>
   <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_escape_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_sweep_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_04</x:t>
+    <x:t>use_ground_escape_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -992,408 +1007,408 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A21" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C21" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
@@ -1401,140 +1416,200 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A23" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C23" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A24" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A25" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C25" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B27" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C27" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A28" s="6" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A29" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A30" s="6" t="s">
         <x:v>23</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="6"/>
-      <x:c r="B28" s="6"/>
-      <x:c r="C28" s="6"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="6"/>
-      <x:c r="B29" s="6"/>
-      <x:c r="C29" s="6"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="6"/>
-      <x:c r="B30" s="6"/>
-      <x:c r="C30" s="6"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="6"/>
-      <x:c r="B31" s="6"/>
-      <x:c r="C31" s="6"/>
+      <x:c r="B30" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A31" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A32" s="6"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -21,202 +21,202 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="66">
   <x:si>
+    <x:t>skill_ground_sweep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_back_control_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_entry_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guard_pass_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_jab_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_escape_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>use_ground_escape_04</x:t>
   </x:si>
   <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>use_ground_escape_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_sweep_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_sweep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_entry_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_back_control_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guard_pass_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_sweep_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_escape_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_jab_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wrestling</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_escape_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_escape_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -987,7 +987,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I37"/>
+  <x:dimension ref="A1:J38"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="2" width="25.4296875" style="1" customWidth="1"/>
@@ -1007,328 +1007,334 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6" ht="15.75" customHeight="1">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
@@ -1336,279 +1342,279 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A21" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C21" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A22" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C22" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A23" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C23" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A24" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A25" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C25" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B26" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B27" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C28" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A29" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C29" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A30" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B30" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C30" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A31" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B31" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C31" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
@@ -1636,12 +1642,19 @@
       <x:c r="B36" s="3"/>
       <x:c r="C36" s="3"/>
     </x:row>
-    <x:row r="37" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="37" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A37" s="3"/>
       <x:c r="B37" s="3"/>
       <x:c r="C37" s="3"/>
-    </x:row>
-    <x:row r="38" ht="15.75" customHeight="1"/>
+      <x:c r="E37" s="3"/>
+      <x:c r="F37" s="3"/>
+      <x:c r="G37" s="3"/>
+    </x:row>
+    <x:row r="38" spans="5:7" ht="15.75" customHeight="1">
+      <x:c r="E38" s="3"/>
+      <x:c r="F38" s="3"/>
+      <x:c r="G38" s="3"/>
+    </x:row>
     <x:row r="39" ht="15.75" customHeight="1"/>
     <x:row r="40" ht="15.75" customHeight="1"/>
     <x:row r="41" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillUseConditionData.xlsx
@@ -19,204 +19,222 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="66">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="72">
+  <x:si>
+    <x:t>use_kick_high_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_kick_middle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Top</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
   <x:si>
     <x:t>skill_ground_sweep</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_guard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_sweep_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_back_control_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_entry_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_judo</x:t>
+  </x:si>
+  <x:si>
     <x:t>use_ground_sweep_02</x:t>
   </x:si>
   <x:si>
-    <x:t>use_back_control_01</x:t>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guard_pass_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_guillotine_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
   </x:si>
   <x:si>
     <x:t>skill_back_control</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_sweep_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_entry_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_judo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guard_pass_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_guillotine_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Top</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>Defender</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_elbow_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_uppercut_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MatchSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_high</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_middle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bottom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Clinch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bottom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UserRole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Defender</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TakedownAttempt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_elbow_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_uppercut_02</x:t>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Attacker</x:t>
   </x:si>
   <x:si>
     <x:t>use_jab_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Attacker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_jab</x:t>
   </x:si>
   <x:si>
-    <x:t>Wrestling</x:t>
+    <x:t>use_ground_escape_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_takedown_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_basic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_02</x:t>
   </x:si>
   <x:si>
     <x:t>use_ground_pounding_03</x:t>
   </x:si>
   <x:si>
+    <x:t>use_takedown_judo_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_escape_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_ground_pounding_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_takedown_judo_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>use_clinch_escape_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_ground_pounding</x:t>
   </x:si>
   <x:si>
-    <x:t>use_takedown_basic_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_clinch_escape_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_escape_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_takedown_judo_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_escape_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_escape_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_pounding_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>use_ground_escape_02</x:t>
+    <x:t>use_kick_low_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_low</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1007,128 +1025,128 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H7" s="3"/>
       <x:c r="I7" s="3"/>
@@ -1139,19 +1157,19 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="3"/>
       <x:c r="I8" s="3"/>
@@ -1159,422 +1177,422 @@
     </x:row>
     <x:row r="9" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A21" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A22" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C22" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A23" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C23" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A24" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C24" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A25" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B25" s="5" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C25" s="5" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B26" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C26" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B27" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C27" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A29" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
@@ -1582,55 +1600,100 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B30" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A31" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="6"/>
-      <x:c r="B32" s="6"/>
-      <x:c r="C32" s="6"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="6"/>
-      <x:c r="B33" s="6"/>
-      <x:c r="C33" s="6"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="3"/>
-      <x:c r="B34" s="3"/>
-      <x:c r="C34" s="3"/>
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A32" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A33" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A34" s="3" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B34" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A35" s="3"/>
